--- a/artfynd/A 33699-2022 artfynd.xlsx
+++ b/artfynd/A 33699-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33699-2022 artfynd.xlsx
+++ b/artfynd/A 33699-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82220110</v>
+        <v>103835032</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stora Uvberget, Srm</t>
+          <t>Myskbergen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576168.9424578277</v>
+        <v>576580</v>
       </c>
       <c r="R2" t="n">
-        <v>6568917.759308658</v>
+        <v>6568853</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +751,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-07-09</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-09-03</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Växer på fin hällmark.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,69 +786,71 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lilian Karlsson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91120349</v>
+        <v>103865937</v>
       </c>
       <c r="B3" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Myskan, Myskan, Srm</t>
+          <t>Myskbergen, Myskan, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576390.6854620975</v>
+        <v>576433</v>
       </c>
       <c r="R3" t="n">
-        <v>6568950.856263433</v>
+        <v>6568877</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +874,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-04-30</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-04-30</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,80 +902,85 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Hällmark</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sara Elg</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Elg</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103843109</v>
+        <v>82219999</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Myskbergen, Myskan, Srm</t>
+          <t>Stora Uvberget, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576382.8916879557</v>
+        <v>576255</v>
       </c>
       <c r="R4" t="n">
-        <v>6568905.170871881</v>
+        <v>6568930</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,27 +1004,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2019-09-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ca 30 plantor, men fler knärot bör eftersökas då det är lämplig växtmiljö. Skogen är avverkningsanmäld.</t>
+          <t>2019-09-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,44 +1018,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Hällmark, lätt skuggig fuktig skogsmiljö med äldre granar och blåbärsris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103866041</v>
+        <v>82220001</v>
       </c>
       <c r="B5" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1060,46 +1047,44 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Myskbergen, Myskan, Srm</t>
+          <t>Stora Uvberget, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576375.8947560196</v>
+        <v>576592</v>
       </c>
       <c r="R5" t="n">
-        <v>6568896.333713895</v>
+        <v>6568910</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,22 +1108,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,47 +1122,623 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Hällmark</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>103865883</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Myskbergen, Myskan, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>576527</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6568889</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-09-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-09-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Fjäder av tjädertupp.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Hällmark med gammal tall</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Michael Lander</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Michael Lander</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>103866041</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Myskbergen, Myskan, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>576376</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6568896</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-09-30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-09-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Hällmark</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>103843109</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Myskbergen, Myskan, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>576383</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6568905</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-09-30</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-09-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca 30 plantor, men fler knärot bör eftersökas då det är lämplig växtmiljö. Skogen är avverkningsanmäld.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Hällmark, lätt skuggig fuktig skogsmiljö med äldre granar och blåbärsris</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>91120349</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Myskan, Myskan, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>576391</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6568951</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-04-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-04-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>82220110</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stora Uvberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>576169</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6568918</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2019-07-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2019-09-03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33699-2022 artfynd.xlsx
+++ b/artfynd/A 33699-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103835032</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103865937</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1033,6 +1048,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82219999</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1137,6 +1157,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82220001</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1263,6 +1288,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103865883</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1405,6 +1435,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103866041</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1540,6 +1575,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103843109</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1642,6 +1682,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91120349</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1739,8 +1784,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82220110</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>